--- a/output/pdf_financials_xlsx/TICO.xlsx
+++ b/output/pdf_financials_xlsx/TICO.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004775</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002976</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001831</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.141678</v>
+        <v>-0.146453</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.066009</v>
+        <v>-0.068985</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.036769</v>
+        <v>-0.0386</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.141678</v>
+        <v>-0.146453</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.066009</v>
+        <v>-0.068985</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.036769</v>
+        <v>-0.0386</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.058514</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005765</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.004491</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.058514</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005765</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.004491</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.08691599999999999</v>
+        <v>0.028402</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.034146</v>
+        <v>0.028381</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.008074</v>
+        <v>0.003583</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">

--- a/output/pdf_financials_xlsx/TICO.xlsx
+++ b/output/pdf_financials_xlsx/TICO.xlsx
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="68">
